--- a/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/03_Rechtekette_Vertraege/08_Rechtekettenmatrix.xlsx
+++ b/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/03_Rechtekette_Vertraege/08_Rechtekettenmatrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rechtekette" sheetId="1" r:id="Rd90b27e6b7f74b73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fassungen" sheetId="2" r:id="R3eaa619c026146d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rechtekette" sheetId="1" r:id="Reec62585aae64378"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fassungen" sheetId="2" r:id="R2eca8946dda6484e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/03_Rechtekette_Vertraege/08_Rechtekettenmatrix.xlsx
+++ b/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/03_Rechtekette_Vertraege/08_Rechtekettenmatrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rechtekette" sheetId="1" r:id="Reec62585aae64378"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fassungen" sheetId="2" r:id="R2eca8946dda6484e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rechtekette" sheetId="1" r:id="R68894b88926f4ec2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fassungen" sheetId="2" r:id="Rd8565d8115c346be"/>
   </x:sheets>
 </x:workbook>
 </file>
